--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.33011726790991</v>
+        <v>6.391144056035361</v>
       </c>
       <c r="D2" t="n">
-        <v>38.84498292887493</v>
+        <v>6.312309725942176</v>
       </c>
       <c r="E2" t="n">
-        <v>14.39607777204358</v>
+        <v>2.339362637957082</v>
       </c>
       <c r="F2" t="n">
-        <v>14.56603970835624</v>
+        <v>2.366981452607889</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.35631487717538</v>
+        <v>1.032901167540999</v>
       </c>
       <c r="D3" t="n">
-        <v>5.913280612353148</v>
+        <v>0.9609080995073865</v>
       </c>
       <c r="E3" t="n">
-        <v>14.39607777204358</v>
+        <v>2.339362637957082</v>
       </c>
       <c r="F3" t="n">
-        <v>14.56603970835624</v>
+        <v>2.366981452607889</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.22467524505138</v>
+        <v>2.474009727320849</v>
       </c>
       <c r="D4" t="n">
-        <v>15.0506224265483</v>
+        <v>2.445726144314099</v>
       </c>
       <c r="E4" t="n">
-        <v>14.39607777204358</v>
+        <v>2.339362637957082</v>
       </c>
       <c r="F4" t="n">
-        <v>14.56603970835624</v>
+        <v>2.366981452607889</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.43866400534845</v>
+        <v>6.246282900869123</v>
       </c>
       <c r="D5" t="n">
-        <v>38.93190333914635</v>
+        <v>6.326434292611283</v>
       </c>
       <c r="E5" t="n">
-        <v>14.39607777204358</v>
+        <v>2.339362637957082</v>
       </c>
       <c r="F5" t="n">
-        <v>14.56603970835624</v>
+        <v>2.366981452607889</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
